--- a/Plannings 2026 S28.xlsx
+++ b/Plannings 2026 S28.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{15FD9598-F048-44A4-8AB2-DEDBCAFB4389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{661953C8-8273-4104-8AFB-DE8C6C8416FC}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{15FD9598-F048-44A4-8AB2-DEDBCAFB4389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD23DD15-2834-43CD-98A8-C137E24A8955}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5801,7 +5801,7 @@
   <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="42.7109375" style="12" customWidth="1"/>
+    <col min="1" max="8" width="41.42578125" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7110,7 +7110,7 @@
     <mergeCell ref="B6:H6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="38" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="39" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -7877,13 +7877,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB8547B6-5978-4AC9-9144-4303096A8128}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{678BE059-4D20-4ACB-A519-E73CE0A47114}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F43E0E8E-E1E4-4E8D-852C-AEA7BF6BF179}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F39E956-8F40-4CAF-87DD-7269CDEA3436}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E562B222-DF4D-4DE3-B7A1-2E025E2875CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDF86E59-6F43-4DEC-80A3-5A529498E295}"/>
 </file>
--- a/Plannings 2026 S28.xlsx
+++ b/Plannings 2026 S28.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{15FD9598-F048-44A4-8AB2-DEDBCAFB4389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD23DD15-2834-43CD-98A8-C137E24A8955}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{15FD9598-F048-44A4-8AB2-DEDBCAFB4389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{661953C8-8273-4104-8AFB-DE8C6C8416FC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5801,7 +5801,7 @@
   <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="41.42578125" style="12" customWidth="1"/>
+    <col min="1" max="8" width="42.7109375" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7110,7 +7110,7 @@
     <mergeCell ref="B6:H6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="39" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="38" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -7877,13 +7877,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{678BE059-4D20-4ACB-A519-E73CE0A47114}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB8547B6-5978-4AC9-9144-4303096A8128}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F39E956-8F40-4CAF-87DD-7269CDEA3436}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F43E0E8E-E1E4-4E8D-852C-AEA7BF6BF179}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDF86E59-6F43-4DEC-80A3-5A529498E295}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E562B222-DF4D-4DE3-B7A1-2E025E2875CF}"/>
 </file>
--- a/Plannings 2026 S28.xlsx
+++ b/Plannings 2026 S28.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{15FD9598-F048-44A4-8AB2-DEDBCAFB4389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD23DD15-2834-43CD-98A8-C137E24A8955}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{15FD9598-F048-44A4-8AB2-DEDBCAFB4389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A2A6279-0C97-47BC-829F-474CBE023578}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="109">
   <si>
     <t>Planning des salariés du 06/07/2026 au 12/07/2026</t>
   </si>
@@ -213,6 +213,9 @@
     <t>FREIXEDAS-BERENGUER Maxime</t>
   </si>
   <si>
+    <t>16:00/18:00</t>
+  </si>
+  <si>
     <t>GACHET Melissa</t>
   </si>
   <si>
@@ -343,6 +346,9 @@
   </si>
   <si>
     <t>CUP PADEL BBQ</t>
+  </si>
+  <si>
+    <t>18:00/19:00</t>
   </si>
 </sst>
 </file>
@@ -476,7 +482,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -753,11 +759,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -913,6 +932,9 @@
     <xf numFmtId="11" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="11" fontId="2" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3450,197 +3472,2001 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{196D552E-3D7A-4FCE-8F7F-C83BC4E9A667}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14231471" y="3697941"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>42</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E2F5DB0-95CD-4803-B6BC-877962DB1F0C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3656,1767 +5482,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{196D552E-3D7A-4FCE-8F7F-C83BC4E9A667}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14231471" y="3697941"/>
+          <a:off x="13811250" y="10844893"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5798,7 +5864,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="41.42578125" style="12" customWidth="1"/>
@@ -5828,19 +5894,19 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>49</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G3" s="14"/>
       <c r="H3" s="14"/>
@@ -6483,140 +6549,124 @@
       <c r="G41" s="26"/>
       <c r="H41" s="27"/>
     </row>
-    <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="31"/>
-      <c r="B42" s="44"/>
-      <c r="C42" s="44" t="s">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="53"/>
+      <c r="B42" s="42"/>
+      <c r="C42" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="44"/>
-      <c r="E42" s="44" t="s">
+      <c r="D42" s="42"/>
+      <c r="E42" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="F42" s="44"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="33"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="27"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="B43" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C43" s="23"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F43" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G43" s="23"/>
-      <c r="H43" s="24" t="s">
-        <v>14</v>
-      </c>
+      <c r="A43" s="53"/>
+      <c r="B43" s="42"/>
+      <c r="C43" s="42"/>
+      <c r="D43" s="42"/>
+      <c r="E43" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="F43" s="42"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="27"/>
     </row>
     <row r="44" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="31"/>
-      <c r="B44" s="32" t="s">
+      <c r="B44" s="44"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="F44" s="44"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="33"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B45" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="23"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F45" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" s="23"/>
+      <c r="H45" s="24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="31"/>
+      <c r="B46" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="C44" s="32"/>
-      <c r="D44" s="32"/>
-      <c r="E44" s="32" t="s">
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="F44" s="32" t="s">
+      <c r="F46" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="G44" s="32"/>
-      <c r="H44" s="33" t="s">
+      <c r="G46" s="32"/>
+      <c r="H46" s="33" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="B45" s="19"/>
-      <c r="C45" s="20"/>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="21"/>
-    </row>
-    <row r="46" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="15" t="s">
+    <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="B46" s="19"/>
-      <c r="C46" s="20"/>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="20"/>
-      <c r="H46" s="21"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="45" t="s">
+      <c r="B47" s="19"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="21"/>
+    </row>
+    <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="B47" s="42" t="s">
+      <c r="B48" s="19"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
+      <c r="H48" s="21"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="45" t="s">
+        <v>66</v>
+      </c>
+      <c r="B49" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="C47" s="42" t="s">
+      <c r="C49" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="D47" s="42" t="s">
+      <c r="D49" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="E47" s="42" t="s">
+      <c r="E49" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="F47" s="42" t="s">
+      <c r="F49" s="42" t="s">
         <v>49</v>
-      </c>
-      <c r="G47" s="26"/>
-      <c r="H47" s="27"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="25"/>
-      <c r="B48" s="42" t="s">
-        <v>50</v>
-      </c>
-      <c r="C48" s="42" t="s">
-        <v>50</v>
-      </c>
-      <c r="D48" s="42" t="s">
-        <v>50</v>
-      </c>
-      <c r="E48" s="42" t="s">
-        <v>50</v>
-      </c>
-      <c r="F48" s="42" t="s">
-        <v>50</v>
-      </c>
-      <c r="G48" s="26"/>
-      <c r="H48" s="27"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="25"/>
-      <c r="B49" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="C49" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="D49" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="E49" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="F49" s="43" t="s">
-        <v>51</v>
       </c>
       <c r="G49" s="26"/>
       <c r="H49" s="27"/>
@@ -6624,19 +6674,19 @@
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="25"/>
       <c r="B50" s="42" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C50" s="42" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D50" s="42" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E50" s="42" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F50" s="42" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G50" s="26"/>
       <c r="H50" s="27"/>
@@ -6644,19 +6694,19 @@
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="25"/>
       <c r="B51" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C51" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D51" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E51" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F51" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G51" s="26"/>
       <c r="H51" s="27"/>
@@ -6664,19 +6714,19 @@
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="25"/>
       <c r="B52" s="42" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C52" s="42" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="D52" s="42" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="E52" s="42" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="F52" s="42" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G52" s="26"/>
       <c r="H52" s="27"/>
@@ -6684,19 +6734,19 @@
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="25"/>
       <c r="B53" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C53" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D53" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E53" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F53" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G53" s="26"/>
       <c r="H53" s="27"/>
@@ -6704,19 +6754,19 @@
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="25"/>
       <c r="B54" s="42" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C54" s="42" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D54" s="42" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E54" s="42" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F54" s="42" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="G54" s="26"/>
       <c r="H54" s="27"/>
@@ -6724,19 +6774,19 @@
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="25"/>
       <c r="B55" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C55" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D55" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E55" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F55" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G55" s="26"/>
       <c r="H55" s="27"/>
@@ -6744,19 +6794,19 @@
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="25"/>
       <c r="B56" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C56" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D56" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E56" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F56" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G56" s="26"/>
       <c r="H56" s="27"/>
@@ -6764,290 +6814,306 @@
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="25"/>
       <c r="B57" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="C57" s="42"/>
+        <v>49</v>
+      </c>
+      <c r="C57" s="43" t="s">
+        <v>49</v>
+      </c>
       <c r="D57" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="E57" s="42"/>
-      <c r="F57" s="42"/>
+        <v>49</v>
+      </c>
+      <c r="E57" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="F57" s="43" t="s">
+        <v>49</v>
+      </c>
       <c r="G57" s="26"/>
       <c r="H57" s="27"/>
     </row>
-    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="31"/>
-      <c r="B58" s="44" t="s">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="25"/>
+      <c r="B58" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="C58" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="D58" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="E58" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="F58" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="G58" s="26"/>
+      <c r="H58" s="27"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="25"/>
+      <c r="B59" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C59" s="42"/>
+      <c r="D59" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="E59" s="42"/>
+      <c r="F59" s="42"/>
+      <c r="G59" s="26"/>
+      <c r="H59" s="27"/>
+    </row>
+    <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="31"/>
+      <c r="B60" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="C58" s="44"/>
-      <c r="D58" s="44" t="s">
+      <c r="C60" s="44"/>
+      <c r="D60" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="E58" s="44"/>
-      <c r="F58" s="44"/>
-      <c r="G58" s="32"/>
-      <c r="H58" s="33"/>
-    </row>
-    <row r="59" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="B59" s="19"/>
-      <c r="C59" s="20"/>
-      <c r="D59" s="20"/>
-      <c r="E59" s="20"/>
-      <c r="F59" s="20"/>
-      <c r="G59" s="20"/>
-      <c r="H59" s="21"/>
-    </row>
-    <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="15" t="s">
+      <c r="E60" s="44"/>
+      <c r="F60" s="44"/>
+      <c r="G60" s="32"/>
+      <c r="H60" s="33"/>
+    </row>
+    <row r="61" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="B60" s="19"/>
-      <c r="C60" s="20"/>
-      <c r="D60" s="20"/>
-      <c r="E60" s="20"/>
-      <c r="F60" s="20"/>
-      <c r="G60" s="20"/>
-      <c r="H60" s="21"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="22" t="s">
+      <c r="B61" s="19"/>
+      <c r="C61" s="20"/>
+      <c r="D61" s="20"/>
+      <c r="E61" s="20"/>
+      <c r="F61" s="20"/>
+      <c r="G61" s="20"/>
+      <c r="H61" s="21"/>
+    </row>
+    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="B61" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C61" s="23"/>
-      <c r="D61" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E61" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="F61" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G61" s="23"/>
-      <c r="H61" s="24"/>
-    </row>
-    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="31"/>
-      <c r="B62" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C62" s="32"/>
-      <c r="D62" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="E62" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="F62" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="G62" s="32"/>
-      <c r="H62" s="33"/>
+      <c r="B62" s="19"/>
+      <c r="C62" s="20"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="20"/>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20"/>
+      <c r="H62" s="21"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63" s="23"/>
+      <c r="D63" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="F63" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G63" s="23"/>
+      <c r="H63" s="24"/>
+    </row>
+    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="31"/>
+      <c r="B64" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C64" s="32"/>
+      <c r="D64" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="E64" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="B63" s="23"/>
-      <c r="C63" s="23"/>
-      <c r="D63" s="23"/>
-      <c r="E63" s="23"/>
-      <c r="F63" s="23"/>
-      <c r="G63" s="47" t="s">
+      <c r="F64" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="G64" s="32"/>
+      <c r="H64" s="33"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="H63" s="24"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="25"/>
-      <c r="B64" s="26"/>
-      <c r="C64" s="26"/>
-      <c r="D64" s="26"/>
-      <c r="E64" s="26"/>
-      <c r="F64" s="26"/>
-      <c r="G64" s="48" t="s">
+      <c r="B65" s="23"/>
+      <c r="C65" s="23"/>
+      <c r="D65" s="23"/>
+      <c r="E65" s="23"/>
+      <c r="F65" s="23"/>
+      <c r="G65" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="H64" s="27"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="25"/>
-      <c r="B65" s="26"/>
-      <c r="C65" s="26"/>
-      <c r="D65" s="26"/>
-      <c r="E65" s="26"/>
-      <c r="F65" s="26"/>
-      <c r="G65" s="30" t="s">
+      <c r="H65" s="24"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="25"/>
+      <c r="B66" s="26"/>
+      <c r="C66" s="26"/>
+      <c r="D66" s="26"/>
+      <c r="E66" s="26"/>
+      <c r="F66" s="26"/>
+      <c r="G66" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="H66" s="27"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="25"/>
+      <c r="B67" s="26"/>
+      <c r="C67" s="26"/>
+      <c r="D67" s="26"/>
+      <c r="E67" s="26"/>
+      <c r="F67" s="26"/>
+      <c r="G67" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="H65" s="27"/>
-    </row>
-    <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="31"/>
-      <c r="B66" s="32"/>
-      <c r="C66" s="32"/>
-      <c r="D66" s="32"/>
-      <c r="E66" s="32"/>
-      <c r="F66" s="32"/>
-      <c r="G66" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="H66" s="33"/>
-    </row>
-    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="15" t="s">
+      <c r="H67" s="27"/>
+    </row>
+    <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="31"/>
+      <c r="B68" s="32"/>
+      <c r="C68" s="32"/>
+      <c r="D68" s="32"/>
+      <c r="E68" s="32"/>
+      <c r="F68" s="32"/>
+      <c r="G68" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="B67" s="19"/>
-      <c r="C67" s="20"/>
-      <c r="D67" s="20"/>
-      <c r="E67" s="20"/>
-      <c r="F67" s="20"/>
-      <c r="G67" s="20"/>
-      <c r="H67" s="21"/>
-    </row>
-    <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="15" t="s">
+      <c r="H68" s="33"/>
+    </row>
+    <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="B68" s="19"/>
-      <c r="C68" s="20"/>
-      <c r="D68" s="20"/>
-      <c r="E68" s="20"/>
-      <c r="F68" s="20"/>
-      <c r="G68" s="20"/>
-      <c r="H68" s="21"/>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="22" t="s">
+      <c r="B69" s="19"/>
+      <c r="C69" s="20"/>
+      <c r="D69" s="20"/>
+      <c r="E69" s="20"/>
+      <c r="F69" s="20"/>
+      <c r="G69" s="20"/>
+      <c r="H69" s="21"/>
+    </row>
+    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="B69" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C69" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D69" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E69" s="23"/>
-      <c r="F69" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G69" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H69" s="24"/>
-    </row>
-    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="31"/>
-      <c r="B70" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="C70" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="D70" s="32" t="s">
-        <v>80</v>
-      </c>
-      <c r="E70" s="32"/>
-      <c r="F70" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="G70" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="H70" s="33"/>
+      <c r="B70" s="19"/>
+      <c r="C70" s="20"/>
+      <c r="D70" s="20"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="20"/>
+      <c r="G70" s="20"/>
+      <c r="H70" s="21"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="B71" s="23"/>
+        <v>80</v>
+      </c>
+      <c r="B71" s="23" t="s">
+        <v>14</v>
+      </c>
       <c r="C71" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D71" s="23"/>
+      <c r="D71" s="23" t="s">
+        <v>14</v>
+      </c>
       <c r="E71" s="23"/>
-      <c r="F71" s="23"/>
-      <c r="G71" s="23"/>
-      <c r="H71" s="49" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="25"/>
-      <c r="B72" s="26"/>
-      <c r="C72" s="26" t="s">
+      <c r="F71" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G71" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H71" s="24"/>
+    </row>
+    <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="31"/>
+      <c r="B72" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="C72" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="D72" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="E72" s="32"/>
+      <c r="F72" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="G72" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="H72" s="33"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="D72" s="26"/>
-      <c r="E72" s="26"/>
-      <c r="F72" s="26"/>
-      <c r="G72" s="26"/>
-      <c r="H72" s="50" t="s">
+      <c r="B73" s="23"/>
+      <c r="C73" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D73" s="23"/>
+      <c r="E73" s="23"/>
+      <c r="F73" s="23"/>
+      <c r="G73" s="23"/>
+      <c r="H73" s="49" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="25"/>
-      <c r="B73" s="26"/>
-      <c r="C73" s="26"/>
-      <c r="D73" s="26"/>
-      <c r="E73" s="26"/>
-      <c r="F73" s="26"/>
-      <c r="G73" s="26"/>
-      <c r="H73" s="51" t="s">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="25"/>
+      <c r="B74" s="26"/>
+      <c r="C74" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="D74" s="26"/>
+      <c r="E74" s="26"/>
+      <c r="F74" s="26"/>
+      <c r="G74" s="26"/>
+      <c r="H74" s="50" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="25"/>
+      <c r="B75" s="26"/>
+      <c r="C75" s="26"/>
+      <c r="D75" s="26"/>
+      <c r="E75" s="26"/>
+      <c r="F75" s="26"/>
+      <c r="G75" s="26"/>
+      <c r="H75" s="51" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="31"/>
-      <c r="B74" s="32"/>
-      <c r="C74" s="32"/>
-      <c r="D74" s="32"/>
-      <c r="E74" s="32"/>
-      <c r="F74" s="32"/>
-      <c r="G74" s="32"/>
-      <c r="H74" s="33" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="B75" s="19"/>
-      <c r="C75" s="20"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20"/>
-      <c r="H75" s="21"/>
-    </row>
     <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="B76" s="19"/>
-      <c r="C76" s="20"/>
-      <c r="D76" s="20"/>
-      <c r="E76" s="20"/>
-      <c r="F76" s="20"/>
-      <c r="G76" s="20"/>
-      <c r="H76" s="21"/>
+      <c r="A76" s="31"/>
+      <c r="B76" s="32"/>
+      <c r="C76" s="32"/>
+      <c r="D76" s="32"/>
+      <c r="E76" s="32"/>
+      <c r="F76" s="32"/>
+      <c r="G76" s="32"/>
+      <c r="H76" s="33" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B77" s="19"/>
       <c r="C77" s="20"/>
@@ -7059,7 +7125,7 @@
     </row>
     <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B78" s="19"/>
       <c r="C78" s="20"/>
@@ -7069,37 +7135,61 @@
       <c r="G78" s="20"/>
       <c r="H78" s="21"/>
     </row>
-    <row r="79" spans="1:8" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="52"/>
-      <c r="C79" s="52"/>
-      <c r="D79" s="52"/>
-      <c r="E79" s="52"/>
-      <c r="F79" s="52"/>
-      <c r="G79" s="52"/>
-      <c r="H79" s="52"/>
+    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B79" s="19"/>
+      <c r="C79" s="20"/>
+      <c r="D79" s="20"/>
+      <c r="E79" s="20"/>
+      <c r="F79" s="20"/>
+      <c r="G79" s="20"/>
+      <c r="H79" s="21"/>
+    </row>
+    <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B80" s="19"/>
+      <c r="C80" s="20"/>
+      <c r="D80" s="20"/>
+      <c r="E80" s="20"/>
+      <c r="F80" s="20"/>
+      <c r="G80" s="20"/>
+      <c r="H80" s="21"/>
+    </row>
+    <row r="81" spans="2:8" ht="3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="52"/>
+      <c r="C81" s="52"/>
+      <c r="D81" s="52"/>
+      <c r="E81" s="52"/>
+      <c r="F81" s="52"/>
+      <c r="G81" s="52"/>
+      <c r="H81" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B79:H79"/>
+    <mergeCell ref="B81:H81"/>
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="B28:H28"/>
-    <mergeCell ref="B45:H45"/>
-    <mergeCell ref="B46:H46"/>
-    <mergeCell ref="B60:H60"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B68:H68"/>
-    <mergeCell ref="B67:H67"/>
-    <mergeCell ref="B75:H75"/>
-    <mergeCell ref="B76:H76"/>
+    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B48:H48"/>
+    <mergeCell ref="B62:H62"/>
+    <mergeCell ref="B61:H61"/>
+    <mergeCell ref="B70:H70"/>
+    <mergeCell ref="B69:H69"/>
     <mergeCell ref="B77:H77"/>
     <mergeCell ref="B78:H78"/>
-    <mergeCell ref="A63:A66"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="A71:A74"/>
-    <mergeCell ref="A47:A58"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="A29:A42"/>
-    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B79:H79"/>
+    <mergeCell ref="B80:H80"/>
+    <mergeCell ref="A65:A68"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="A73:A76"/>
+    <mergeCell ref="A49:A60"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="A29:A44"/>
+    <mergeCell ref="A45:A46"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A15:A18"/>
     <mergeCell ref="A20:A27"/>
@@ -7127,7 +7217,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -7135,7 +7225,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
@@ -7146,16 +7236,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7364,7 +7454,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B19" s="5">
         <v>0</v>
@@ -7381,7 +7471,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B20" s="5">
         <v>0</v>
@@ -7398,7 +7488,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B21" s="5">
         <v>0</v>
@@ -7415,7 +7505,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B22" s="5">
         <v>0</v>
@@ -7432,7 +7522,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B23" s="5">
         <v>0</v>
@@ -7449,7 +7539,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B24" s="5">
         <v>0</v>
@@ -7466,7 +7556,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B25" s="5">
         <v>0</v>
@@ -7483,7 +7573,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B26" s="5">
         <v>0</v>
@@ -7500,7 +7590,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B27" s="5">
         <v>0</v>
@@ -7517,7 +7607,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B28" s="5">
         <v>0</v>
@@ -7534,7 +7624,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B29" s="5">
         <v>0</v>
@@ -7551,7 +7641,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B30" s="5">
         <v>0</v>
@@ -7568,7 +7658,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B31" s="5">
         <v>0</v>
@@ -7585,7 +7675,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B32" s="5">
         <v>0</v>
@@ -7602,7 +7692,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B33" s="5">
         <v>0</v>
@@ -7619,7 +7709,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B34" s="5">
         <v>0</v>
@@ -7669,40 +7759,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B5" s="9"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -7877,13 +7967,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{678BE059-4D20-4ACB-A519-E73CE0A47114}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{447690ED-FE51-4BC2-A737-5C4F0F17E4C0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F39E956-8F40-4CAF-87DD-7269CDEA3436}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4A8B831-C67D-4F25-8D7B-6C5856AAD81B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDF86E59-6F43-4DEC-80A3-5A529498E295}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4D18E04-D7D6-476D-AF35-243A06A051CE}"/>
 </file>
--- a/Plannings 2026 S28.xlsx
+++ b/Plannings 2026 S28.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{15FD9598-F048-44A4-8AB2-DEDBCAFB4389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A2A6279-0C97-47BC-829F-474CBE023578}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{15FD9598-F048-44A4-8AB2-DEDBCAFB4389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{661953C8-8273-4104-8AFB-DE8C6C8416FC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="107">
   <si>
     <t>Planning des salariés du 06/07/2026 au 12/07/2026</t>
   </si>
@@ -213,9 +213,6 @@
     <t>FREIXEDAS-BERENGUER Maxime</t>
   </si>
   <si>
-    <t>16:00/18:00</t>
-  </si>
-  <si>
     <t>GACHET Melissa</t>
   </si>
   <si>
@@ -346,9 +343,6 @@
   </si>
   <si>
     <t>CUP PADEL BBQ</t>
-  </si>
-  <si>
-    <t>18:00/19:00</t>
   </si>
 </sst>
 </file>
@@ -482,7 +476,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -759,24 +753,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -932,9 +913,6 @@
     <xf numFmtId="11" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="2" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3472,13 +3450,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3516,13 +3494,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3560,13 +3538,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3604,13 +3582,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3648,6 +3626,50 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>48</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -3659,10 +3681,54 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3692,206 +3758,1306 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>50</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3912,30 +5078,162 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3956,646 +5254,118 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4616,241 +5386,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{196D552E-3D7A-4FCE-8F7F-C83BC4E9A667}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4866,623 +5416,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{196D552E-3D7A-4FCE-8F7F-C83BC4E9A667}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
           <a:off x="14231471" y="3697941"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E2F5DB0-95CD-4803-B6BC-877962DB1F0C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13811250" y="10844893"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5864,10 +5798,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="41.42578125" style="12" customWidth="1"/>
+    <col min="1" max="8" width="42.7109375" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5894,19 +5828,19 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>49</v>
       </c>
       <c r="D3" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="E3" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="F3" s="14" t="s">
         <v>106</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>107</v>
       </c>
       <c r="G3" s="14"/>
       <c r="H3" s="14"/>
@@ -6549,124 +6483,140 @@
       <c r="G41" s="26"/>
       <c r="H41" s="27"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="53"/>
-      <c r="B42" s="42"/>
-      <c r="C42" s="42" t="s">
+    <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="31"/>
+      <c r="B42" s="44"/>
+      <c r="C42" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="42"/>
-      <c r="E42" s="42" t="s">
+      <c r="D42" s="44"/>
+      <c r="E42" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="F42" s="42"/>
-      <c r="G42" s="26"/>
-      <c r="H42" s="27"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="33"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="53"/>
-      <c r="B43" s="42"/>
-      <c r="C43" s="42"/>
-      <c r="D43" s="42"/>
-      <c r="E43" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="F43" s="42"/>
-      <c r="G43" s="26"/>
-      <c r="H43" s="27"/>
+      <c r="A43" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F43" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" s="23"/>
+      <c r="H43" s="24" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="44" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="31"/>
-      <c r="B44" s="44"/>
-      <c r="C44" s="44"/>
-      <c r="D44" s="44"/>
-      <c r="E44" s="42" t="s">
-        <v>108</v>
-      </c>
-      <c r="F44" s="44"/>
+      <c r="B44" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F44" s="32" t="s">
+        <v>60</v>
+      </c>
       <c r="G44" s="32"/>
-      <c r="H44" s="33"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="B45" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C45" s="23"/>
-      <c r="D45" s="23"/>
-      <c r="E45" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F45" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G45" s="23"/>
-      <c r="H45" s="24" t="s">
-        <v>14</v>
-      </c>
+      <c r="H44" s="33" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="B45" s="19"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="21"/>
     </row>
     <row r="46" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="31"/>
-      <c r="B46" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="C46" s="32"/>
-      <c r="D46" s="32"/>
-      <c r="E46" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="F46" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="G46" s="32"/>
-      <c r="H46" s="33" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="15" t="s">
+      <c r="A46" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="B47" s="19"/>
-      <c r="C47" s="20"/>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20"/>
-      <c r="H47" s="21"/>
-    </row>
-    <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="15" t="s">
+      <c r="B46" s="19"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="21"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="B48" s="19"/>
-      <c r="C48" s="20"/>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="20"/>
-      <c r="H48" s="21"/>
+      <c r="B47" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="C47" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="D47" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="E47" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="F47" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="G47" s="26"/>
+      <c r="H47" s="27"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="25"/>
+      <c r="B48" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="C48" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="D48" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="E48" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="F48" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="G48" s="26"/>
+      <c r="H48" s="27"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="45" t="s">
-        <v>66</v>
-      </c>
-      <c r="B49" s="42" t="s">
-        <v>49</v>
-      </c>
-      <c r="C49" s="42" t="s">
-        <v>49</v>
-      </c>
-      <c r="D49" s="42" t="s">
-        <v>49</v>
-      </c>
-      <c r="E49" s="42" t="s">
-        <v>49</v>
-      </c>
-      <c r="F49" s="42" t="s">
-        <v>49</v>
+      <c r="A49" s="25"/>
+      <c r="B49" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C49" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="D49" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="E49" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="F49" s="43" t="s">
+        <v>51</v>
       </c>
       <c r="G49" s="26"/>
       <c r="H49" s="27"/>
@@ -6674,19 +6624,19 @@
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="25"/>
       <c r="B50" s="42" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C50" s="42" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D50" s="42" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E50" s="42" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F50" s="42" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G50" s="26"/>
       <c r="H50" s="27"/>
@@ -6694,19 +6644,19 @@
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="25"/>
       <c r="B51" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C51" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D51" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E51" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F51" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G51" s="26"/>
       <c r="H51" s="27"/>
@@ -6714,19 +6664,19 @@
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="25"/>
       <c r="B52" s="42" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C52" s="42" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D52" s="42" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="E52" s="42" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="F52" s="42" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="G52" s="26"/>
       <c r="H52" s="27"/>
@@ -6734,19 +6684,19 @@
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="25"/>
       <c r="B53" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C53" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D53" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E53" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F53" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G53" s="26"/>
       <c r="H53" s="27"/>
@@ -6754,19 +6704,19 @@
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="25"/>
       <c r="B54" s="42" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C54" s="42" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D54" s="42" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="E54" s="42" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="F54" s="42" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="G54" s="26"/>
       <c r="H54" s="27"/>
@@ -6774,19 +6724,19 @@
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="25"/>
       <c r="B55" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C55" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D55" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E55" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F55" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G55" s="26"/>
       <c r="H55" s="27"/>
@@ -6794,19 +6744,19 @@
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="25"/>
       <c r="B56" s="42" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C56" s="42" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D56" s="42" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E56" s="42" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F56" s="42" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G56" s="26"/>
       <c r="H56" s="27"/>
@@ -6814,306 +6764,290 @@
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="25"/>
       <c r="B57" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="C57" s="43" t="s">
-        <v>49</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="C57" s="42"/>
       <c r="D57" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="E57" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="F57" s="43" t="s">
-        <v>49</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="E57" s="42"/>
+      <c r="F57" s="42"/>
       <c r="G57" s="26"/>
       <c r="H57" s="27"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="25"/>
-      <c r="B58" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="C58" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="D58" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="E58" s="42" t="s">
-        <v>63</v>
-      </c>
-      <c r="F58" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="G58" s="26"/>
-      <c r="H58" s="27"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="25"/>
-      <c r="B59" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="C59" s="42"/>
-      <c r="D59" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="E59" s="42"/>
-      <c r="F59" s="42"/>
-      <c r="G59" s="26"/>
-      <c r="H59" s="27"/>
+    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="31"/>
+      <c r="B58" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="C58" s="44"/>
+      <c r="D58" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="E58" s="44"/>
+      <c r="F58" s="44"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="33"/>
+    </row>
+    <row r="59" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B59" s="19"/>
+      <c r="C59" s="20"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="20"/>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20"/>
+      <c r="H59" s="21"/>
     </row>
     <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="31"/>
-      <c r="B60" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="C60" s="44"/>
-      <c r="D60" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="E60" s="44"/>
-      <c r="F60" s="44"/>
-      <c r="G60" s="32"/>
-      <c r="H60" s="33"/>
-    </row>
-    <row r="61" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="15" t="s">
+      <c r="A60" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="B61" s="19"/>
-      <c r="C61" s="20"/>
-      <c r="D61" s="20"/>
-      <c r="E61" s="20"/>
-      <c r="F61" s="20"/>
-      <c r="G61" s="20"/>
-      <c r="H61" s="21"/>
+      <c r="B60" s="19"/>
+      <c r="C60" s="20"/>
+      <c r="D60" s="20"/>
+      <c r="E60" s="20"/>
+      <c r="F60" s="20"/>
+      <c r="G60" s="20"/>
+      <c r="H60" s="21"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61" s="23"/>
+      <c r="D61" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="F61" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G61" s="23"/>
+      <c r="H61" s="24"/>
     </row>
     <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B62" s="19"/>
-      <c r="C62" s="20"/>
-      <c r="D62" s="20"/>
-      <c r="E62" s="20"/>
-      <c r="F62" s="20"/>
-      <c r="G62" s="20"/>
-      <c r="H62" s="21"/>
+      <c r="A62" s="31"/>
+      <c r="B62" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C62" s="32"/>
+      <c r="D62" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="E62" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="F62" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="G62" s="32"/>
+      <c r="H62" s="33"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="B63" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="B63" s="23"/>
+      <c r="C63" s="23"/>
+      <c r="D63" s="23"/>
+      <c r="E63" s="23"/>
+      <c r="F63" s="23"/>
+      <c r="G63" s="47" t="s">
+        <v>74</v>
+      </c>
+      <c r="H63" s="24"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="25"/>
+      <c r="B64" s="26"/>
+      <c r="C64" s="26"/>
+      <c r="D64" s="26"/>
+      <c r="E64" s="26"/>
+      <c r="F64" s="26"/>
+      <c r="G64" s="48" t="s">
+        <v>75</v>
+      </c>
+      <c r="H64" s="27"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="25"/>
+      <c r="B65" s="26"/>
+      <c r="C65" s="26"/>
+      <c r="D65" s="26"/>
+      <c r="E65" s="26"/>
+      <c r="F65" s="26"/>
+      <c r="G65" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="C63" s="23"/>
-      <c r="D63" s="23" t="s">
+      <c r="H65" s="27"/>
+    </row>
+    <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="31"/>
+      <c r="B66" s="32"/>
+      <c r="C66" s="32"/>
+      <c r="D66" s="32"/>
+      <c r="E66" s="32"/>
+      <c r="F66" s="32"/>
+      <c r="G66" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="H66" s="33"/>
+    </row>
+    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B67" s="19"/>
+      <c r="C67" s="20"/>
+      <c r="D67" s="20"/>
+      <c r="E67" s="20"/>
+      <c r="F67" s="20"/>
+      <c r="G67" s="20"/>
+      <c r="H67" s="21"/>
+    </row>
+    <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B68" s="19"/>
+      <c r="C68" s="20"/>
+      <c r="D68" s="20"/>
+      <c r="E68" s="20"/>
+      <c r="F68" s="20"/>
+      <c r="G68" s="20"/>
+      <c r="H68" s="21"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="B69" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E63" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="F63" s="23" t="s">
+      <c r="C69" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G63" s="23"/>
-      <c r="H63" s="24"/>
-    </row>
-    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="31"/>
-      <c r="B64" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C64" s="32"/>
-      <c r="D64" s="32" t="s">
-        <v>72</v>
-      </c>
-      <c r="E64" s="36" t="s">
-        <v>73</v>
-      </c>
-      <c r="F64" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="G64" s="32"/>
-      <c r="H64" s="33"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="B65" s="23"/>
-      <c r="C65" s="23"/>
-      <c r="D65" s="23"/>
-      <c r="E65" s="23"/>
-      <c r="F65" s="23"/>
-      <c r="G65" s="47" t="s">
-        <v>75</v>
-      </c>
-      <c r="H65" s="24"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="25"/>
-      <c r="B66" s="26"/>
-      <c r="C66" s="26"/>
-      <c r="D66" s="26"/>
-      <c r="E66" s="26"/>
-      <c r="F66" s="26"/>
-      <c r="G66" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="H66" s="27"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="25"/>
-      <c r="B67" s="26"/>
-      <c r="C67" s="26"/>
-      <c r="D67" s="26"/>
-      <c r="E67" s="26"/>
-      <c r="F67" s="26"/>
-      <c r="G67" s="30" t="s">
+      <c r="D69" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H67" s="27"/>
-    </row>
-    <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="31"/>
-      <c r="B68" s="32"/>
-      <c r="C68" s="32"/>
-      <c r="D68" s="32"/>
-      <c r="E68" s="32"/>
-      <c r="F68" s="32"/>
-      <c r="G68" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="H68" s="33"/>
-    </row>
-    <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="B69" s="19"/>
-      <c r="C69" s="20"/>
-      <c r="D69" s="20"/>
-      <c r="E69" s="20"/>
-      <c r="F69" s="20"/>
-      <c r="G69" s="20"/>
-      <c r="H69" s="21"/>
+      <c r="E69" s="23"/>
+      <c r="F69" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G69" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H69" s="24"/>
     </row>
     <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B70" s="19"/>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
-      <c r="H70" s="21"/>
+      <c r="A70" s="31"/>
+      <c r="B70" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="C70" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="D70" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="E70" s="32"/>
+      <c r="F70" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="G70" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="H70" s="33"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="B71" s="23" t="s">
-        <v>14</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="B71" s="23"/>
       <c r="C71" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D71" s="23" t="s">
+      <c r="D71" s="23"/>
+      <c r="E71" s="23"/>
+      <c r="F71" s="23"/>
+      <c r="G71" s="23"/>
+      <c r="H71" s="49" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="25"/>
+      <c r="B72" s="26"/>
+      <c r="C72" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="D72" s="26"/>
+      <c r="E72" s="26"/>
+      <c r="F72" s="26"/>
+      <c r="G72" s="26"/>
+      <c r="H72" s="50" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="25"/>
+      <c r="B73" s="26"/>
+      <c r="C73" s="26"/>
+      <c r="D73" s="26"/>
+      <c r="E73" s="26"/>
+      <c r="F73" s="26"/>
+      <c r="G73" s="26"/>
+      <c r="H73" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="E71" s="23"/>
-      <c r="F71" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G71" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H71" s="24"/>
-    </row>
-    <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="31"/>
-      <c r="B72" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="C72" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="D72" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="E72" s="32"/>
-      <c r="F72" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="G72" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="H72" s="33"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="B73" s="23"/>
-      <c r="C73" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D73" s="23"/>
-      <c r="E73" s="23"/>
-      <c r="F73" s="23"/>
-      <c r="G73" s="23"/>
-      <c r="H73" s="49" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="25"/>
-      <c r="B74" s="26"/>
-      <c r="C74" s="26" t="s">
+    </row>
+    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="31"/>
+      <c r="B74" s="32"/>
+      <c r="C74" s="32"/>
+      <c r="D74" s="32"/>
+      <c r="E74" s="32"/>
+      <c r="F74" s="32"/>
+      <c r="G74" s="32"/>
+      <c r="H74" s="33" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="D74" s="26"/>
-      <c r="E74" s="26"/>
-      <c r="F74" s="26"/>
-      <c r="G74" s="26"/>
-      <c r="H74" s="50" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="25"/>
-      <c r="B75" s="26"/>
-      <c r="C75" s="26"/>
-      <c r="D75" s="26"/>
-      <c r="E75" s="26"/>
-      <c r="F75" s="26"/>
-      <c r="G75" s="26"/>
-      <c r="H75" s="51" t="s">
-        <v>14</v>
-      </c>
+      <c r="B75" s="19"/>
+      <c r="C75" s="20"/>
+      <c r="D75" s="20"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="20"/>
+      <c r="G75" s="20"/>
+      <c r="H75" s="21"/>
     </row>
     <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="31"/>
-      <c r="B76" s="32"/>
-      <c r="C76" s="32"/>
-      <c r="D76" s="32"/>
-      <c r="E76" s="32"/>
-      <c r="F76" s="32"/>
-      <c r="G76" s="32"/>
-      <c r="H76" s="33" t="s">
-        <v>77</v>
-      </c>
+      <c r="A76" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B76" s="19"/>
+      <c r="C76" s="20"/>
+      <c r="D76" s="20"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20"/>
+      <c r="G76" s="20"/>
+      <c r="H76" s="21"/>
     </row>
     <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B77" s="19"/>
       <c r="C77" s="20"/>
@@ -7125,7 +7059,7 @@
     </row>
     <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B78" s="19"/>
       <c r="C78" s="20"/>
@@ -7135,61 +7069,37 @@
       <c r="G78" s="20"/>
       <c r="H78" s="21"/>
     </row>
-    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B79" s="19"/>
-      <c r="C79" s="20"/>
-      <c r="D79" s="20"/>
-      <c r="E79" s="20"/>
-      <c r="F79" s="20"/>
-      <c r="G79" s="20"/>
-      <c r="H79" s="21"/>
-    </row>
-    <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="B80" s="19"/>
-      <c r="C80" s="20"/>
-      <c r="D80" s="20"/>
-      <c r="E80" s="20"/>
-      <c r="F80" s="20"/>
-      <c r="G80" s="20"/>
-      <c r="H80" s="21"/>
-    </row>
-    <row r="81" spans="2:8" ht="3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="52"/>
-      <c r="C81" s="52"/>
-      <c r="D81" s="52"/>
-      <c r="E81" s="52"/>
-      <c r="F81" s="52"/>
-      <c r="G81" s="52"/>
-      <c r="H81" s="52"/>
+    <row r="79" spans="1:8" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="52"/>
+      <c r="C79" s="52"/>
+      <c r="D79" s="52"/>
+      <c r="E79" s="52"/>
+      <c r="F79" s="52"/>
+      <c r="G79" s="52"/>
+      <c r="H79" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B81:H81"/>
+    <mergeCell ref="B79:H79"/>
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="B28:H28"/>
-    <mergeCell ref="B47:H47"/>
-    <mergeCell ref="B48:H48"/>
-    <mergeCell ref="B62:H62"/>
-    <mergeCell ref="B61:H61"/>
-    <mergeCell ref="B70:H70"/>
-    <mergeCell ref="B69:H69"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="B60:H60"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B68:H68"/>
+    <mergeCell ref="B67:H67"/>
+    <mergeCell ref="B75:H75"/>
+    <mergeCell ref="B76:H76"/>
     <mergeCell ref="B77:H77"/>
     <mergeCell ref="B78:H78"/>
-    <mergeCell ref="B79:H79"/>
-    <mergeCell ref="B80:H80"/>
-    <mergeCell ref="A65:A68"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="A73:A76"/>
-    <mergeCell ref="A49:A60"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="A29:A44"/>
-    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A63:A66"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="A71:A74"/>
+    <mergeCell ref="A47:A58"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="A29:A42"/>
+    <mergeCell ref="A43:A44"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A15:A18"/>
     <mergeCell ref="A20:A27"/>
@@ -7200,7 +7110,7 @@
     <mergeCell ref="B6:H6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="39" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="38" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -7217,7 +7127,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -7225,7 +7135,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
@@ -7236,16 +7146,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7454,7 +7364,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B19" s="5">
         <v>0</v>
@@ -7471,7 +7381,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B20" s="5">
         <v>0</v>
@@ -7488,7 +7398,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B21" s="5">
         <v>0</v>
@@ -7505,7 +7415,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B22" s="5">
         <v>0</v>
@@ -7522,7 +7432,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B23" s="5">
         <v>0</v>
@@ -7539,7 +7449,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B24" s="5">
         <v>0</v>
@@ -7556,7 +7466,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B25" s="5">
         <v>0</v>
@@ -7573,7 +7483,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B26" s="5">
         <v>0</v>
@@ -7590,7 +7500,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B27" s="5">
         <v>0</v>
@@ -7607,7 +7517,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B28" s="5">
         <v>0</v>
@@ -7624,7 +7534,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B29" s="5">
         <v>0</v>
@@ -7641,7 +7551,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B30" s="5">
         <v>0</v>
@@ -7658,7 +7568,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B31" s="5">
         <v>0</v>
@@ -7675,7 +7585,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B32" s="5">
         <v>0</v>
@@ -7692,7 +7602,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B33" s="5">
         <v>0</v>
@@ -7709,7 +7619,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B34" s="5">
         <v>0</v>
@@ -7759,40 +7669,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>96</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B5" s="9"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>100</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>102</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -7967,13 +7877,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{447690ED-FE51-4BC2-A737-5C4F0F17E4C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB8547B6-5978-4AC9-9144-4303096A8128}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4A8B831-C67D-4F25-8D7B-6C5856AAD81B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F43E0E8E-E1E4-4E8D-852C-AEA7BF6BF179}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4D18E04-D7D6-476D-AF35-243A06A051CE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E562B222-DF4D-4DE3-B7A1-2E025E2875CF}"/>
 </file>
--- a/Plannings 2026 S28.xlsx
+++ b/Plannings 2026 S28.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{15FD9598-F048-44A4-8AB2-DEDBCAFB4389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{661953C8-8273-4104-8AFB-DE8C6C8416FC}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{15FD9598-F048-44A4-8AB2-DEDBCAFB4389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A2A6279-0C97-47BC-829F-474CBE023578}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="109">
   <si>
     <t>Planning des salariés du 06/07/2026 au 12/07/2026</t>
   </si>
@@ -213,6 +213,9 @@
     <t>FREIXEDAS-BERENGUER Maxime</t>
   </si>
   <si>
+    <t>16:00/18:00</t>
+  </si>
+  <si>
     <t>GACHET Melissa</t>
   </si>
   <si>
@@ -343,6 +346,9 @@
   </si>
   <si>
     <t>CUP PADEL BBQ</t>
+  </si>
+  <si>
+    <t>18:00/19:00</t>
   </si>
 </sst>
 </file>
@@ -476,7 +482,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -753,11 +759,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -913,6 +932,9 @@
     <xf numFmtId="11" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="11" fontId="2" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3450,197 +3472,2001 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{196D552E-3D7A-4FCE-8F7F-C83BC4E9A667}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14231471" y="3697941"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>42</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E2F5DB0-95CD-4803-B6BC-877962DB1F0C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3656,1767 +5482,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{196D552E-3D7A-4FCE-8F7F-C83BC4E9A667}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14231471" y="3697941"/>
+          <a:off x="13811250" y="10844893"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5798,10 +5864,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="42.7109375" style="12" customWidth="1"/>
+    <col min="1" max="8" width="41.42578125" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5828,19 +5894,19 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>49</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G3" s="14"/>
       <c r="H3" s="14"/>
@@ -6483,140 +6549,124 @@
       <c r="G41" s="26"/>
       <c r="H41" s="27"/>
     </row>
-    <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="31"/>
-      <c r="B42" s="44"/>
-      <c r="C42" s="44" t="s">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="53"/>
+      <c r="B42" s="42"/>
+      <c r="C42" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="44"/>
-      <c r="E42" s="44" t="s">
+      <c r="D42" s="42"/>
+      <c r="E42" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="F42" s="44"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="33"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="27"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="B43" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C43" s="23"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F43" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G43" s="23"/>
-      <c r="H43" s="24" t="s">
-        <v>14</v>
-      </c>
+      <c r="A43" s="53"/>
+      <c r="B43" s="42"/>
+      <c r="C43" s="42"/>
+      <c r="D43" s="42"/>
+      <c r="E43" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="F43" s="42"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="27"/>
     </row>
     <row r="44" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="31"/>
-      <c r="B44" s="32" t="s">
+      <c r="B44" s="44"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="F44" s="44"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="33"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B45" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="23"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F45" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" s="23"/>
+      <c r="H45" s="24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="31"/>
+      <c r="B46" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="C44" s="32"/>
-      <c r="D44" s="32"/>
-      <c r="E44" s="32" t="s">
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="F44" s="32" t="s">
+      <c r="F46" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="G44" s="32"/>
-      <c r="H44" s="33" t="s">
+      <c r="G46" s="32"/>
+      <c r="H46" s="33" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="B45" s="19"/>
-      <c r="C45" s="20"/>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="21"/>
-    </row>
-    <row r="46" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="15" t="s">
+    <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="B46" s="19"/>
-      <c r="C46" s="20"/>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="20"/>
-      <c r="H46" s="21"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="45" t="s">
+      <c r="B47" s="19"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="21"/>
+    </row>
+    <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="B47" s="42" t="s">
+      <c r="B48" s="19"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
+      <c r="H48" s="21"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="45" t="s">
+        <v>66</v>
+      </c>
+      <c r="B49" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="C47" s="42" t="s">
+      <c r="C49" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="D47" s="42" t="s">
+      <c r="D49" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="E47" s="42" t="s">
+      <c r="E49" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="F47" s="42" t="s">
+      <c r="F49" s="42" t="s">
         <v>49</v>
-      </c>
-      <c r="G47" s="26"/>
-      <c r="H47" s="27"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="25"/>
-      <c r="B48" s="42" t="s">
-        <v>50</v>
-      </c>
-      <c r="C48" s="42" t="s">
-        <v>50</v>
-      </c>
-      <c r="D48" s="42" t="s">
-        <v>50</v>
-      </c>
-      <c r="E48" s="42" t="s">
-        <v>50</v>
-      </c>
-      <c r="F48" s="42" t="s">
-        <v>50</v>
-      </c>
-      <c r="G48" s="26"/>
-      <c r="H48" s="27"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="25"/>
-      <c r="B49" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="C49" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="D49" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="E49" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="F49" s="43" t="s">
-        <v>51</v>
       </c>
       <c r="G49" s="26"/>
       <c r="H49" s="27"/>
@@ -6624,19 +6674,19 @@
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="25"/>
       <c r="B50" s="42" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C50" s="42" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D50" s="42" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E50" s="42" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F50" s="42" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G50" s="26"/>
       <c r="H50" s="27"/>
@@ -6644,19 +6694,19 @@
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="25"/>
       <c r="B51" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C51" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D51" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E51" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F51" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G51" s="26"/>
       <c r="H51" s="27"/>
@@ -6664,19 +6714,19 @@
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="25"/>
       <c r="B52" s="42" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C52" s="42" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="D52" s="42" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="E52" s="42" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="F52" s="42" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G52" s="26"/>
       <c r="H52" s="27"/>
@@ -6684,19 +6734,19 @@
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="25"/>
       <c r="B53" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C53" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D53" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E53" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F53" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G53" s="26"/>
       <c r="H53" s="27"/>
@@ -6704,19 +6754,19 @@
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="25"/>
       <c r="B54" s="42" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C54" s="42" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D54" s="42" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E54" s="42" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F54" s="42" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="G54" s="26"/>
       <c r="H54" s="27"/>
@@ -6724,19 +6774,19 @@
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="25"/>
       <c r="B55" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C55" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D55" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E55" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F55" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G55" s="26"/>
       <c r="H55" s="27"/>
@@ -6744,19 +6794,19 @@
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="25"/>
       <c r="B56" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C56" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D56" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E56" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F56" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G56" s="26"/>
       <c r="H56" s="27"/>
@@ -6764,290 +6814,306 @@
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="25"/>
       <c r="B57" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="C57" s="42"/>
+        <v>49</v>
+      </c>
+      <c r="C57" s="43" t="s">
+        <v>49</v>
+      </c>
       <c r="D57" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="E57" s="42"/>
-      <c r="F57" s="42"/>
+        <v>49</v>
+      </c>
+      <c r="E57" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="F57" s="43" t="s">
+        <v>49</v>
+      </c>
       <c r="G57" s="26"/>
       <c r="H57" s="27"/>
     </row>
-    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="31"/>
-      <c r="B58" s="44" t="s">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="25"/>
+      <c r="B58" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="C58" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="D58" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="E58" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="F58" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="G58" s="26"/>
+      <c r="H58" s="27"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="25"/>
+      <c r="B59" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C59" s="42"/>
+      <c r="D59" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="E59" s="42"/>
+      <c r="F59" s="42"/>
+      <c r="G59" s="26"/>
+      <c r="H59" s="27"/>
+    </row>
+    <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="31"/>
+      <c r="B60" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="C58" s="44"/>
-      <c r="D58" s="44" t="s">
+      <c r="C60" s="44"/>
+      <c r="D60" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="E58" s="44"/>
-      <c r="F58" s="44"/>
-      <c r="G58" s="32"/>
-      <c r="H58" s="33"/>
-    </row>
-    <row r="59" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="B59" s="19"/>
-      <c r="C59" s="20"/>
-      <c r="D59" s="20"/>
-      <c r="E59" s="20"/>
-      <c r="F59" s="20"/>
-      <c r="G59" s="20"/>
-      <c r="H59" s="21"/>
-    </row>
-    <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="15" t="s">
+      <c r="E60" s="44"/>
+      <c r="F60" s="44"/>
+      <c r="G60" s="32"/>
+      <c r="H60" s="33"/>
+    </row>
+    <row r="61" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="B60" s="19"/>
-      <c r="C60" s="20"/>
-      <c r="D60" s="20"/>
-      <c r="E60" s="20"/>
-      <c r="F60" s="20"/>
-      <c r="G60" s="20"/>
-      <c r="H60" s="21"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="22" t="s">
+      <c r="B61" s="19"/>
+      <c r="C61" s="20"/>
+      <c r="D61" s="20"/>
+      <c r="E61" s="20"/>
+      <c r="F61" s="20"/>
+      <c r="G61" s="20"/>
+      <c r="H61" s="21"/>
+    </row>
+    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="B61" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C61" s="23"/>
-      <c r="D61" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E61" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="F61" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G61" s="23"/>
-      <c r="H61" s="24"/>
-    </row>
-    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="31"/>
-      <c r="B62" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C62" s="32"/>
-      <c r="D62" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="E62" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="F62" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="G62" s="32"/>
-      <c r="H62" s="33"/>
+      <c r="B62" s="19"/>
+      <c r="C62" s="20"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="20"/>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20"/>
+      <c r="H62" s="21"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63" s="23"/>
+      <c r="D63" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="F63" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G63" s="23"/>
+      <c r="H63" s="24"/>
+    </row>
+    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="31"/>
+      <c r="B64" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C64" s="32"/>
+      <c r="D64" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="E64" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="B63" s="23"/>
-      <c r="C63" s="23"/>
-      <c r="D63" s="23"/>
-      <c r="E63" s="23"/>
-      <c r="F63" s="23"/>
-      <c r="G63" s="47" t="s">
+      <c r="F64" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="G64" s="32"/>
+      <c r="H64" s="33"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="H63" s="24"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="25"/>
-      <c r="B64" s="26"/>
-      <c r="C64" s="26"/>
-      <c r="D64" s="26"/>
-      <c r="E64" s="26"/>
-      <c r="F64" s="26"/>
-      <c r="G64" s="48" t="s">
+      <c r="B65" s="23"/>
+      <c r="C65" s="23"/>
+      <c r="D65" s="23"/>
+      <c r="E65" s="23"/>
+      <c r="F65" s="23"/>
+      <c r="G65" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="H64" s="27"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="25"/>
-      <c r="B65" s="26"/>
-      <c r="C65" s="26"/>
-      <c r="D65" s="26"/>
-      <c r="E65" s="26"/>
-      <c r="F65" s="26"/>
-      <c r="G65" s="30" t="s">
+      <c r="H65" s="24"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="25"/>
+      <c r="B66" s="26"/>
+      <c r="C66" s="26"/>
+      <c r="D66" s="26"/>
+      <c r="E66" s="26"/>
+      <c r="F66" s="26"/>
+      <c r="G66" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="H66" s="27"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="25"/>
+      <c r="B67" s="26"/>
+      <c r="C67" s="26"/>
+      <c r="D67" s="26"/>
+      <c r="E67" s="26"/>
+      <c r="F67" s="26"/>
+      <c r="G67" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="H65" s="27"/>
-    </row>
-    <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="31"/>
-      <c r="B66" s="32"/>
-      <c r="C66" s="32"/>
-      <c r="D66" s="32"/>
-      <c r="E66" s="32"/>
-      <c r="F66" s="32"/>
-      <c r="G66" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="H66" s="33"/>
-    </row>
-    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="15" t="s">
+      <c r="H67" s="27"/>
+    </row>
+    <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="31"/>
+      <c r="B68" s="32"/>
+      <c r="C68" s="32"/>
+      <c r="D68" s="32"/>
+      <c r="E68" s="32"/>
+      <c r="F68" s="32"/>
+      <c r="G68" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="B67" s="19"/>
-      <c r="C67" s="20"/>
-      <c r="D67" s="20"/>
-      <c r="E67" s="20"/>
-      <c r="F67" s="20"/>
-      <c r="G67" s="20"/>
-      <c r="H67" s="21"/>
-    </row>
-    <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="15" t="s">
+      <c r="H68" s="33"/>
+    </row>
+    <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="B68" s="19"/>
-      <c r="C68" s="20"/>
-      <c r="D68" s="20"/>
-      <c r="E68" s="20"/>
-      <c r="F68" s="20"/>
-      <c r="G68" s="20"/>
-      <c r="H68" s="21"/>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="22" t="s">
+      <c r="B69" s="19"/>
+      <c r="C69" s="20"/>
+      <c r="D69" s="20"/>
+      <c r="E69" s="20"/>
+      <c r="F69" s="20"/>
+      <c r="G69" s="20"/>
+      <c r="H69" s="21"/>
+    </row>
+    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="B69" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C69" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D69" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E69" s="23"/>
-      <c r="F69" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G69" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H69" s="24"/>
-    </row>
-    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="31"/>
-      <c r="B70" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="C70" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="D70" s="32" t="s">
-        <v>80</v>
-      </c>
-      <c r="E70" s="32"/>
-      <c r="F70" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="G70" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="H70" s="33"/>
+      <c r="B70" s="19"/>
+      <c r="C70" s="20"/>
+      <c r="D70" s="20"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="20"/>
+      <c r="G70" s="20"/>
+      <c r="H70" s="21"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="B71" s="23"/>
+        <v>80</v>
+      </c>
+      <c r="B71" s="23" t="s">
+        <v>14</v>
+      </c>
       <c r="C71" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D71" s="23"/>
+      <c r="D71" s="23" t="s">
+        <v>14</v>
+      </c>
       <c r="E71" s="23"/>
-      <c r="F71" s="23"/>
-      <c r="G71" s="23"/>
-      <c r="H71" s="49" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="25"/>
-      <c r="B72" s="26"/>
-      <c r="C72" s="26" t="s">
+      <c r="F71" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G71" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H71" s="24"/>
+    </row>
+    <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="31"/>
+      <c r="B72" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="C72" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="D72" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="E72" s="32"/>
+      <c r="F72" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="G72" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="H72" s="33"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="D72" s="26"/>
-      <c r="E72" s="26"/>
-      <c r="F72" s="26"/>
-      <c r="G72" s="26"/>
-      <c r="H72" s="50" t="s">
+      <c r="B73" s="23"/>
+      <c r="C73" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D73" s="23"/>
+      <c r="E73" s="23"/>
+      <c r="F73" s="23"/>
+      <c r="G73" s="23"/>
+      <c r="H73" s="49" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="25"/>
-      <c r="B73" s="26"/>
-      <c r="C73" s="26"/>
-      <c r="D73" s="26"/>
-      <c r="E73" s="26"/>
-      <c r="F73" s="26"/>
-      <c r="G73" s="26"/>
-      <c r="H73" s="51" t="s">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="25"/>
+      <c r="B74" s="26"/>
+      <c r="C74" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="D74" s="26"/>
+      <c r="E74" s="26"/>
+      <c r="F74" s="26"/>
+      <c r="G74" s="26"/>
+      <c r="H74" s="50" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="25"/>
+      <c r="B75" s="26"/>
+      <c r="C75" s="26"/>
+      <c r="D75" s="26"/>
+      <c r="E75" s="26"/>
+      <c r="F75" s="26"/>
+      <c r="G75" s="26"/>
+      <c r="H75" s="51" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="31"/>
-      <c r="B74" s="32"/>
-      <c r="C74" s="32"/>
-      <c r="D74" s="32"/>
-      <c r="E74" s="32"/>
-      <c r="F74" s="32"/>
-      <c r="G74" s="32"/>
-      <c r="H74" s="33" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="B75" s="19"/>
-      <c r="C75" s="20"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20"/>
-      <c r="H75" s="21"/>
-    </row>
     <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="B76" s="19"/>
-      <c r="C76" s="20"/>
-      <c r="D76" s="20"/>
-      <c r="E76" s="20"/>
-      <c r="F76" s="20"/>
-      <c r="G76" s="20"/>
-      <c r="H76" s="21"/>
+      <c r="A76" s="31"/>
+      <c r="B76" s="32"/>
+      <c r="C76" s="32"/>
+      <c r="D76" s="32"/>
+      <c r="E76" s="32"/>
+      <c r="F76" s="32"/>
+      <c r="G76" s="32"/>
+      <c r="H76" s="33" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B77" s="19"/>
       <c r="C77" s="20"/>
@@ -7059,7 +7125,7 @@
     </row>
     <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B78" s="19"/>
       <c r="C78" s="20"/>
@@ -7069,37 +7135,61 @@
       <c r="G78" s="20"/>
       <c r="H78" s="21"/>
     </row>
-    <row r="79" spans="1:8" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="52"/>
-      <c r="C79" s="52"/>
-      <c r="D79" s="52"/>
-      <c r="E79" s="52"/>
-      <c r="F79" s="52"/>
-      <c r="G79" s="52"/>
-      <c r="H79" s="52"/>
+    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B79" s="19"/>
+      <c r="C79" s="20"/>
+      <c r="D79" s="20"/>
+      <c r="E79" s="20"/>
+      <c r="F79" s="20"/>
+      <c r="G79" s="20"/>
+      <c r="H79" s="21"/>
+    </row>
+    <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B80" s="19"/>
+      <c r="C80" s="20"/>
+      <c r="D80" s="20"/>
+      <c r="E80" s="20"/>
+      <c r="F80" s="20"/>
+      <c r="G80" s="20"/>
+      <c r="H80" s="21"/>
+    </row>
+    <row r="81" spans="2:8" ht="3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="52"/>
+      <c r="C81" s="52"/>
+      <c r="D81" s="52"/>
+      <c r="E81" s="52"/>
+      <c r="F81" s="52"/>
+      <c r="G81" s="52"/>
+      <c r="H81" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B79:H79"/>
+    <mergeCell ref="B81:H81"/>
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="B28:H28"/>
-    <mergeCell ref="B45:H45"/>
-    <mergeCell ref="B46:H46"/>
-    <mergeCell ref="B60:H60"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B68:H68"/>
-    <mergeCell ref="B67:H67"/>
-    <mergeCell ref="B75:H75"/>
-    <mergeCell ref="B76:H76"/>
+    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B48:H48"/>
+    <mergeCell ref="B62:H62"/>
+    <mergeCell ref="B61:H61"/>
+    <mergeCell ref="B70:H70"/>
+    <mergeCell ref="B69:H69"/>
     <mergeCell ref="B77:H77"/>
     <mergeCell ref="B78:H78"/>
-    <mergeCell ref="A63:A66"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="A71:A74"/>
-    <mergeCell ref="A47:A58"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="A29:A42"/>
-    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B79:H79"/>
+    <mergeCell ref="B80:H80"/>
+    <mergeCell ref="A65:A68"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="A73:A76"/>
+    <mergeCell ref="A49:A60"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="A29:A44"/>
+    <mergeCell ref="A45:A46"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A15:A18"/>
     <mergeCell ref="A20:A27"/>
@@ -7110,7 +7200,7 @@
     <mergeCell ref="B6:H6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="38" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="39" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -7127,7 +7217,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -7135,7 +7225,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
@@ -7146,16 +7236,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7364,7 +7454,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B19" s="5">
         <v>0</v>
@@ -7381,7 +7471,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B20" s="5">
         <v>0</v>
@@ -7398,7 +7488,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B21" s="5">
         <v>0</v>
@@ -7415,7 +7505,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B22" s="5">
         <v>0</v>
@@ -7432,7 +7522,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B23" s="5">
         <v>0</v>
@@ -7449,7 +7539,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B24" s="5">
         <v>0</v>
@@ -7466,7 +7556,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B25" s="5">
         <v>0</v>
@@ -7483,7 +7573,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B26" s="5">
         <v>0</v>
@@ -7500,7 +7590,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B27" s="5">
         <v>0</v>
@@ -7517,7 +7607,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B28" s="5">
         <v>0</v>
@@ -7534,7 +7624,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B29" s="5">
         <v>0</v>
@@ -7551,7 +7641,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B30" s="5">
         <v>0</v>
@@ -7568,7 +7658,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B31" s="5">
         <v>0</v>
@@ -7585,7 +7675,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B32" s="5">
         <v>0</v>
@@ -7602,7 +7692,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B33" s="5">
         <v>0</v>
@@ -7619,7 +7709,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B34" s="5">
         <v>0</v>
@@ -7669,40 +7759,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B5" s="9"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -7877,13 +7967,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB8547B6-5978-4AC9-9144-4303096A8128}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{447690ED-FE51-4BC2-A737-5C4F0F17E4C0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F43E0E8E-E1E4-4E8D-852C-AEA7BF6BF179}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4A8B831-C67D-4F25-8D7B-6C5856AAD81B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E562B222-DF4D-4DE3-B7A1-2E025E2875CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4D18E04-D7D6-476D-AF35-243A06A051CE}"/>
 </file>
--- a/Plannings 2026 S28.xlsx
+++ b/Plannings 2026 S28.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{15FD9598-F048-44A4-8AB2-DEDBCAFB4389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A2A6279-0C97-47BC-829F-474CBE023578}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{15FD9598-F048-44A4-8AB2-DEDBCAFB4389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE36CC31-4733-4533-A274-8BBB65054804}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="108">
   <si>
     <t>Planning des salariés du 06/07/2026 au 12/07/2026</t>
   </si>
@@ -346,9 +346,6 @@
   </si>
   <si>
     <t>CUP PADEL BBQ</t>
-  </si>
-  <si>
-    <t>18:00/19:00</t>
   </si>
 </sst>
 </file>
@@ -3472,13 +3469,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3516,13 +3513,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3560,13 +3557,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3604,13 +3601,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3648,6 +3645,50 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>48</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -3659,10 +3700,54 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3692,206 +3777,1306 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>50</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3912,30 +5097,162 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3956,646 +5273,118 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4616,241 +5405,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{196D552E-3D7A-4FCE-8F7F-C83BC4E9A667}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4866,623 +5435,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{196D552E-3D7A-4FCE-8F7F-C83BC4E9A667}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
           <a:off x="14231471" y="3697941"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E2F5DB0-95CD-4803-B6BC-877962DB1F0C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13811250" y="10844893"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5864,7 +5817,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="41.42578125" style="12" customWidth="1"/>
@@ -6524,7 +6477,7 @@
         <v>56</v>
       </c>
       <c r="D40" s="42" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E40" s="42" t="s">
         <v>56</v>
@@ -6549,7 +6502,7 @@
       <c r="G41" s="26"/>
       <c r="H41" s="27"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="53"/>
       <c r="B42" s="42"/>
       <c r="C42" s="42" t="s">
@@ -6564,109 +6517,125 @@
       <c r="H42" s="27"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="53"/>
-      <c r="B43" s="42"/>
-      <c r="C43" s="42"/>
-      <c r="D43" s="42"/>
-      <c r="E43" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="F43" s="42"/>
-      <c r="G43" s="26"/>
-      <c r="H43" s="27"/>
+      <c r="A43" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F43" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" s="23"/>
+      <c r="H43" s="24" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="44" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="31"/>
-      <c r="B44" s="44"/>
-      <c r="C44" s="44"/>
-      <c r="D44" s="44"/>
-      <c r="E44" s="42" t="s">
-        <v>108</v>
-      </c>
-      <c r="F44" s="44"/>
+      <c r="B44" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F44" s="32" t="s">
+        <v>60</v>
+      </c>
       <c r="G44" s="32"/>
-      <c r="H44" s="33"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="B45" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C45" s="23"/>
-      <c r="D45" s="23"/>
-      <c r="E45" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F45" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G45" s="23"/>
-      <c r="H45" s="24" t="s">
-        <v>14</v>
-      </c>
+      <c r="H44" s="33" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B45" s="19"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="21"/>
     </row>
     <row r="46" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="31"/>
-      <c r="B46" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="C46" s="32"/>
-      <c r="D46" s="32"/>
-      <c r="E46" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="F46" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="G46" s="32"/>
-      <c r="H46" s="33" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="B47" s="19"/>
-      <c r="C47" s="20"/>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20"/>
-      <c r="H47" s="21"/>
-    </row>
-    <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="15" t="s">
+      <c r="A46" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="B48" s="19"/>
-      <c r="C48" s="20"/>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="20"/>
-      <c r="H48" s="21"/>
+      <c r="B46" s="19"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="21"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="45" t="s">
+        <v>66</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="C47" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="D47" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="E47" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="F47" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="G47" s="26"/>
+      <c r="H47" s="27"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="25"/>
+      <c r="B48" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="C48" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="D48" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="E48" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="F48" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="G48" s="26"/>
+      <c r="H48" s="27"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="45" t="s">
-        <v>66</v>
-      </c>
-      <c r="B49" s="42" t="s">
-        <v>49</v>
-      </c>
-      <c r="C49" s="42" t="s">
-        <v>49</v>
-      </c>
-      <c r="D49" s="42" t="s">
-        <v>49</v>
-      </c>
-      <c r="E49" s="42" t="s">
-        <v>49</v>
-      </c>
-      <c r="F49" s="42" t="s">
-        <v>49</v>
+      <c r="A49" s="25"/>
+      <c r="B49" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C49" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="D49" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="E49" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="F49" s="43" t="s">
+        <v>51</v>
       </c>
       <c r="G49" s="26"/>
       <c r="H49" s="27"/>
@@ -6674,19 +6643,19 @@
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="25"/>
       <c r="B50" s="42" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C50" s="42" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D50" s="42" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E50" s="42" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F50" s="42" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G50" s="26"/>
       <c r="H50" s="27"/>
@@ -6694,19 +6663,19 @@
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="25"/>
       <c r="B51" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C51" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D51" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E51" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F51" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G51" s="26"/>
       <c r="H51" s="27"/>
@@ -6714,19 +6683,19 @@
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="25"/>
       <c r="B52" s="42" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C52" s="42" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D52" s="42" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E52" s="42" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F52" s="42" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="G52" s="26"/>
       <c r="H52" s="27"/>
@@ -6734,19 +6703,19 @@
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="25"/>
       <c r="B53" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C53" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D53" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E53" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F53" s="43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G53" s="26"/>
       <c r="H53" s="27"/>
@@ -6754,19 +6723,19 @@
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="25"/>
       <c r="B54" s="42" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C54" s="42" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D54" s="42" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="E54" s="42" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="F54" s="42" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="G54" s="26"/>
       <c r="H54" s="27"/>
@@ -6774,19 +6743,19 @@
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="25"/>
       <c r="B55" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C55" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D55" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E55" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F55" s="43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G55" s="26"/>
       <c r="H55" s="27"/>
@@ -6794,19 +6763,19 @@
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="25"/>
       <c r="B56" s="42" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C56" s="42" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D56" s="42" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E56" s="42" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F56" s="42" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G56" s="26"/>
       <c r="H56" s="27"/>
@@ -6814,306 +6783,290 @@
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="25"/>
       <c r="B57" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="C57" s="43" t="s">
-        <v>49</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="C57" s="42"/>
       <c r="D57" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="E57" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="F57" s="43" t="s">
-        <v>49</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="E57" s="42"/>
+      <c r="F57" s="42"/>
       <c r="G57" s="26"/>
       <c r="H57" s="27"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="25"/>
-      <c r="B58" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="C58" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="D58" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="E58" s="42" t="s">
-        <v>63</v>
-      </c>
-      <c r="F58" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="G58" s="26"/>
-      <c r="H58" s="27"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="25"/>
-      <c r="B59" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="C59" s="42"/>
-      <c r="D59" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="E59" s="42"/>
-      <c r="F59" s="42"/>
-      <c r="G59" s="26"/>
-      <c r="H59" s="27"/>
+    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="31"/>
+      <c r="B58" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="C58" s="44"/>
+      <c r="D58" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="E58" s="44"/>
+      <c r="F58" s="44"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="33"/>
+    </row>
+    <row r="59" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B59" s="19"/>
+      <c r="C59" s="20"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="20"/>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20"/>
+      <c r="H59" s="21"/>
     </row>
     <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="31"/>
-      <c r="B60" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="C60" s="44"/>
-      <c r="D60" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="E60" s="44"/>
-      <c r="F60" s="44"/>
-      <c r="G60" s="32"/>
-      <c r="H60" s="33"/>
-    </row>
-    <row r="61" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="B61" s="19"/>
-      <c r="C61" s="20"/>
-      <c r="D61" s="20"/>
-      <c r="E61" s="20"/>
-      <c r="F61" s="20"/>
-      <c r="G61" s="20"/>
-      <c r="H61" s="21"/>
+      <c r="A60" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B60" s="19"/>
+      <c r="C60" s="20"/>
+      <c r="D60" s="20"/>
+      <c r="E60" s="20"/>
+      <c r="F60" s="20"/>
+      <c r="G60" s="20"/>
+      <c r="H60" s="21"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B61" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61" s="23"/>
+      <c r="D61" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="F61" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G61" s="23"/>
+      <c r="H61" s="24"/>
     </row>
     <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B62" s="19"/>
-      <c r="C62" s="20"/>
-      <c r="D62" s="20"/>
-      <c r="E62" s="20"/>
-      <c r="F62" s="20"/>
-      <c r="G62" s="20"/>
-      <c r="H62" s="21"/>
+      <c r="A62" s="31"/>
+      <c r="B62" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C62" s="32"/>
+      <c r="D62" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="E62" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="F62" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="G62" s="32"/>
+      <c r="H62" s="33"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="B63" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B63" s="23"/>
+      <c r="C63" s="23"/>
+      <c r="D63" s="23"/>
+      <c r="E63" s="23"/>
+      <c r="F63" s="23"/>
+      <c r="G63" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="H63" s="24"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="25"/>
+      <c r="B64" s="26"/>
+      <c r="C64" s="26"/>
+      <c r="D64" s="26"/>
+      <c r="E64" s="26"/>
+      <c r="F64" s="26"/>
+      <c r="G64" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="H64" s="27"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="25"/>
+      <c r="B65" s="26"/>
+      <c r="C65" s="26"/>
+      <c r="D65" s="26"/>
+      <c r="E65" s="26"/>
+      <c r="F65" s="26"/>
+      <c r="G65" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="C63" s="23"/>
-      <c r="D63" s="23" t="s">
+      <c r="H65" s="27"/>
+    </row>
+    <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="31"/>
+      <c r="B66" s="32"/>
+      <c r="C66" s="32"/>
+      <c r="D66" s="32"/>
+      <c r="E66" s="32"/>
+      <c r="F66" s="32"/>
+      <c r="G66" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="H66" s="33"/>
+    </row>
+    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B67" s="19"/>
+      <c r="C67" s="20"/>
+      <c r="D67" s="20"/>
+      <c r="E67" s="20"/>
+      <c r="F67" s="20"/>
+      <c r="G67" s="20"/>
+      <c r="H67" s="21"/>
+    </row>
+    <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B68" s="19"/>
+      <c r="C68" s="20"/>
+      <c r="D68" s="20"/>
+      <c r="E68" s="20"/>
+      <c r="F68" s="20"/>
+      <c r="G68" s="20"/>
+      <c r="H68" s="21"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B69" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E63" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="F63" s="23" t="s">
+      <c r="C69" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G63" s="23"/>
-      <c r="H63" s="24"/>
-    </row>
-    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="31"/>
-      <c r="B64" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C64" s="32"/>
-      <c r="D64" s="32" t="s">
-        <v>72</v>
-      </c>
-      <c r="E64" s="36" t="s">
-        <v>73</v>
-      </c>
-      <c r="F64" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="G64" s="32"/>
-      <c r="H64" s="33"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="B65" s="23"/>
-      <c r="C65" s="23"/>
-      <c r="D65" s="23"/>
-      <c r="E65" s="23"/>
-      <c r="F65" s="23"/>
-      <c r="G65" s="47" t="s">
-        <v>75</v>
-      </c>
-      <c r="H65" s="24"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="25"/>
-      <c r="B66" s="26"/>
-      <c r="C66" s="26"/>
-      <c r="D66" s="26"/>
-      <c r="E66" s="26"/>
-      <c r="F66" s="26"/>
-      <c r="G66" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="H66" s="27"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="25"/>
-      <c r="B67" s="26"/>
-      <c r="C67" s="26"/>
-      <c r="D67" s="26"/>
-      <c r="E67" s="26"/>
-      <c r="F67" s="26"/>
-      <c r="G67" s="30" t="s">
+      <c r="D69" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H67" s="27"/>
-    </row>
-    <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="31"/>
-      <c r="B68" s="32"/>
-      <c r="C68" s="32"/>
-      <c r="D68" s="32"/>
-      <c r="E68" s="32"/>
-      <c r="F68" s="32"/>
-      <c r="G68" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="H68" s="33"/>
-    </row>
-    <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="B69" s="19"/>
-      <c r="C69" s="20"/>
-      <c r="D69" s="20"/>
-      <c r="E69" s="20"/>
-      <c r="F69" s="20"/>
-      <c r="G69" s="20"/>
-      <c r="H69" s="21"/>
+      <c r="E69" s="23"/>
+      <c r="F69" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G69" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H69" s="24"/>
     </row>
     <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B70" s="19"/>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
-      <c r="H70" s="21"/>
+      <c r="A70" s="31"/>
+      <c r="B70" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="C70" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="D70" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="E70" s="32"/>
+      <c r="F70" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="G70" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="H70" s="33"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="B71" s="23" t="s">
-        <v>14</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="B71" s="23"/>
       <c r="C71" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D71" s="23" t="s">
+      <c r="D71" s="23"/>
+      <c r="E71" s="23"/>
+      <c r="F71" s="23"/>
+      <c r="G71" s="23"/>
+      <c r="H71" s="49" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="25"/>
+      <c r="B72" s="26"/>
+      <c r="C72" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="D72" s="26"/>
+      <c r="E72" s="26"/>
+      <c r="F72" s="26"/>
+      <c r="G72" s="26"/>
+      <c r="H72" s="50" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="25"/>
+      <c r="B73" s="26"/>
+      <c r="C73" s="26"/>
+      <c r="D73" s="26"/>
+      <c r="E73" s="26"/>
+      <c r="F73" s="26"/>
+      <c r="G73" s="26"/>
+      <c r="H73" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="E71" s="23"/>
-      <c r="F71" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G71" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H71" s="24"/>
-    </row>
-    <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="31"/>
-      <c r="B72" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="C72" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="D72" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="E72" s="32"/>
-      <c r="F72" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="G72" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="H72" s="33"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="B73" s="23"/>
-      <c r="C73" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D73" s="23"/>
-      <c r="E73" s="23"/>
-      <c r="F73" s="23"/>
-      <c r="G73" s="23"/>
-      <c r="H73" s="49" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="25"/>
-      <c r="B74" s="26"/>
-      <c r="C74" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="D74" s="26"/>
-      <c r="E74" s="26"/>
-      <c r="F74" s="26"/>
-      <c r="G74" s="26"/>
-      <c r="H74" s="50" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="25"/>
-      <c r="B75" s="26"/>
-      <c r="C75" s="26"/>
-      <c r="D75" s="26"/>
-      <c r="E75" s="26"/>
-      <c r="F75" s="26"/>
-      <c r="G75" s="26"/>
-      <c r="H75" s="51" t="s">
-        <v>14</v>
-      </c>
+    </row>
+    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="31"/>
+      <c r="B74" s="32"/>
+      <c r="C74" s="32"/>
+      <c r="D74" s="32"/>
+      <c r="E74" s="32"/>
+      <c r="F74" s="32"/>
+      <c r="G74" s="32"/>
+      <c r="H74" s="33" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B75" s="19"/>
+      <c r="C75" s="20"/>
+      <c r="D75" s="20"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="20"/>
+      <c r="G75" s="20"/>
+      <c r="H75" s="21"/>
     </row>
     <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="31"/>
-      <c r="B76" s="32"/>
-      <c r="C76" s="32"/>
-      <c r="D76" s="32"/>
-      <c r="E76" s="32"/>
-      <c r="F76" s="32"/>
-      <c r="G76" s="32"/>
-      <c r="H76" s="33" t="s">
-        <v>77</v>
-      </c>
+      <c r="A76" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B76" s="19"/>
+      <c r="C76" s="20"/>
+      <c r="D76" s="20"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20"/>
+      <c r="G76" s="20"/>
+      <c r="H76" s="21"/>
     </row>
     <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="15" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B77" s="19"/>
       <c r="C77" s="20"/>
@@ -7125,7 +7078,7 @@
     </row>
     <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B78" s="19"/>
       <c r="C78" s="20"/>
@@ -7135,61 +7088,37 @@
       <c r="G78" s="20"/>
       <c r="H78" s="21"/>
     </row>
-    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B79" s="19"/>
-      <c r="C79" s="20"/>
-      <c r="D79" s="20"/>
-      <c r="E79" s="20"/>
-      <c r="F79" s="20"/>
-      <c r="G79" s="20"/>
-      <c r="H79" s="21"/>
-    </row>
-    <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="B80" s="19"/>
-      <c r="C80" s="20"/>
-      <c r="D80" s="20"/>
-      <c r="E80" s="20"/>
-      <c r="F80" s="20"/>
-      <c r="G80" s="20"/>
-      <c r="H80" s="21"/>
-    </row>
-    <row r="81" spans="2:8" ht="3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="52"/>
-      <c r="C81" s="52"/>
-      <c r="D81" s="52"/>
-      <c r="E81" s="52"/>
-      <c r="F81" s="52"/>
-      <c r="G81" s="52"/>
-      <c r="H81" s="52"/>
+    <row r="79" spans="1:8" ht="3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="52"/>
+      <c r="C79" s="52"/>
+      <c r="D79" s="52"/>
+      <c r="E79" s="52"/>
+      <c r="F79" s="52"/>
+      <c r="G79" s="52"/>
+      <c r="H79" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B81:H81"/>
+    <mergeCell ref="B79:H79"/>
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="B28:H28"/>
-    <mergeCell ref="B47:H47"/>
-    <mergeCell ref="B48:H48"/>
-    <mergeCell ref="B62:H62"/>
-    <mergeCell ref="B61:H61"/>
-    <mergeCell ref="B70:H70"/>
-    <mergeCell ref="B69:H69"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="B60:H60"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B68:H68"/>
+    <mergeCell ref="B67:H67"/>
+    <mergeCell ref="B75:H75"/>
+    <mergeCell ref="B76:H76"/>
     <mergeCell ref="B77:H77"/>
     <mergeCell ref="B78:H78"/>
-    <mergeCell ref="B79:H79"/>
-    <mergeCell ref="B80:H80"/>
-    <mergeCell ref="A65:A68"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="A73:A76"/>
-    <mergeCell ref="A49:A60"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="A29:A44"/>
-    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A63:A66"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="A71:A74"/>
+    <mergeCell ref="A47:A58"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="A29:A42"/>
+    <mergeCell ref="A43:A44"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A15:A18"/>
     <mergeCell ref="A20:A27"/>
@@ -7967,13 +7896,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{447690ED-FE51-4BC2-A737-5C4F0F17E4C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4382DA25-75D5-413B-B0BD-3BD23835BC6A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4A8B831-C67D-4F25-8D7B-6C5856AAD81B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16914D10-A219-4B9F-BC6F-81576BC5DAA9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4D18E04-D7D6-476D-AF35-243A06A051CE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10284400-D0C0-4492-B31B-BD6B0255FCBF}"/>
 </file>
--- a/Plannings 2026 S28.xlsx
+++ b/Plannings 2026 S28.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{15FD9598-F048-44A4-8AB2-DEDBCAFB4389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE36CC31-4733-4533-A274-8BBB65054804}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{15FD9598-F048-44A4-8AB2-DEDBCAFB4389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00C653B9-5295-49FF-8B1E-DEDC7D0D1167}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -468,13 +468,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCC99FF"/>
+        <fgColor rgb="FFCCFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCFFFF"/>
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -893,34 +893,22 @@
     <xf numFmtId="11" fontId="4" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="4" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="4" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="4" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="4" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="4" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="4" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="15" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="15" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="15" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="15" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -930,6 +918,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="2" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="15" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="15" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="15" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="15" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6503,7 +6503,7 @@
       <c r="H41" s="27"/>
     </row>
     <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="53"/>
+      <c r="A42" s="49"/>
       <c r="B42" s="42"/>
       <c r="C42" s="42" t="s">
         <v>57</v>
@@ -6879,7 +6879,7 @@
       <c r="D63" s="23"/>
       <c r="E63" s="23"/>
       <c r="F63" s="23"/>
-      <c r="G63" s="47" t="s">
+      <c r="G63" s="50" t="s">
         <v>75</v>
       </c>
       <c r="H63" s="24"/>
@@ -6891,7 +6891,7 @@
       <c r="D64" s="26"/>
       <c r="E64" s="26"/>
       <c r="F64" s="26"/>
-      <c r="G64" s="48" t="s">
+      <c r="G64" s="51" t="s">
         <v>76</v>
       </c>
       <c r="H64" s="27"/>
@@ -6998,7 +6998,7 @@
       <c r="E71" s="23"/>
       <c r="F71" s="23"/>
       <c r="G71" s="23"/>
-      <c r="H71" s="49" t="s">
+      <c r="H71" s="52" t="s">
         <v>75</v>
       </c>
     </row>
@@ -7012,7 +7012,7 @@
       <c r="E72" s="26"/>
       <c r="F72" s="26"/>
       <c r="G72" s="26"/>
-      <c r="H72" s="50" t="s">
+      <c r="H72" s="53" t="s">
         <v>76</v>
       </c>
     </row>
@@ -7024,7 +7024,7 @@
       <c r="E73" s="26"/>
       <c r="F73" s="26"/>
       <c r="G73" s="26"/>
-      <c r="H73" s="51" t="s">
+      <c r="H73" s="47" t="s">
         <v>14</v>
       </c>
     </row>
@@ -7089,13 +7089,13 @@
       <c r="H78" s="21"/>
     </row>
     <row r="79" spans="1:8" ht="3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="52"/>
-      <c r="C79" s="52"/>
-      <c r="D79" s="52"/>
-      <c r="E79" s="52"/>
-      <c r="F79" s="52"/>
-      <c r="G79" s="52"/>
-      <c r="H79" s="52"/>
+      <c r="B79" s="48"/>
+      <c r="C79" s="48"/>
+      <c r="D79" s="48"/>
+      <c r="E79" s="48"/>
+      <c r="F79" s="48"/>
+      <c r="G79" s="48"/>
+      <c r="H79" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -7896,13 +7896,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4382DA25-75D5-413B-B0BD-3BD23835BC6A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3039D80A-3E46-4C5A-AD01-A91AE601E8FB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16914D10-A219-4B9F-BC6F-81576BC5DAA9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE6E0854-29AB-4B15-BD99-E5B8C52089C5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10284400-D0C0-4492-B31B-BD6B0255FCBF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{462E07BE-DA17-404D-9C5A-C23996E1878E}"/>
 </file>